--- a/data-manipulation-scripts/sheets-cleanup/sheets/CHAVE DE LUZ 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CHAVE DE LUZ 03_02.xlsx
@@ -136,7 +136,7 @@
     <t>7899248147393</t>
   </si>
   <si>
-    <t>CHAVE LUZ  LADO ESQUERDO CONDOR CTZ CROSSER150 2015 A 2016</t>
+    <t>CHAVE LUZ  LADO ESQUERDO CONDOR XTZ CROSSER150 2015 A 2016</t>
   </si>
   <si>
     <t>618341656956</t>
@@ -205,7 +205,7 @@
     <t>CHAVE LUZ TMAC PCX150 2016 A 2018</t>
   </si>
   <si>
-    <t>PUNHO LUZ CB250 TWISTER</t>
+    <t>PUNHO LUZ RT CB250 TWISTER</t>
   </si>
   <si>
     <t>7898905501530</t>
@@ -529,7 +529,9 @@
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>80.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -609,7 +611,9 @@
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="2">
+        <v>65.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -621,7 +625,9 @@
       <c r="C9" s="2">
         <v>2.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>65.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -647,7 +653,9 @@
       <c r="C11" s="2">
         <v>1.0</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="2">
+        <v>85.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -674,7 +682,7 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="2">
-        <v>10.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="14">
@@ -687,7 +695,9 @@
       <c r="C14" s="2">
         <v>1.0</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="2">
+        <v>105.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3"/>
@@ -711,7 +721,9 @@
       <c r="C16" s="2">
         <v>2.0</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="2">
+        <v>58.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
@@ -723,7 +735,9 @@
       <c r="C17" s="2">
         <v>6.0</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="2">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
@@ -735,7 +749,9 @@
       <c r="C18" s="2">
         <v>2.0</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="2">
+        <v>58.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
@@ -747,7 +763,9 @@
       <c r="C19" s="2">
         <v>2.0</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="2">
+        <v>66.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
@@ -759,7 +777,9 @@
       <c r="C20" s="2">
         <v>2.0</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="2">
+        <v>62.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
@@ -771,7 +791,9 @@
       <c r="C21" s="2">
         <v>2.0</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="2">
+        <v>85.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
@@ -783,7 +805,9 @@
       <c r="C22" s="2">
         <v>3.0</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="2">
+        <v>75.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
@@ -795,7 +819,9 @@
       <c r="C23" s="2">
         <v>1.0</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="2">
+        <v>58.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
@@ -807,7 +833,9 @@
       <c r="C24" s="2">
         <v>1.0</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="2">
+        <v>58.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
@@ -819,7 +847,9 @@
       <c r="C25" s="2">
         <v>1.0</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="2">
+        <v>85.0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
@@ -831,7 +861,9 @@
       <c r="C26" s="2">
         <v>1.0</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="2">
+        <v>58.0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
@@ -843,7 +875,9 @@
       <c r="C27" s="2">
         <v>1.0</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="2">
+        <v>75.0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
@@ -855,7 +889,9 @@
       <c r="C28" s="2">
         <v>1.0</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="2">
+        <v>90.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
@@ -867,7 +903,9 @@
       <c r="C29" s="2">
         <v>1.0</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="2">
+        <v>110.0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
@@ -879,7 +917,9 @@
       <c r="C30" s="2">
         <v>1.0</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="2">
+        <v>83.0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
@@ -891,7 +931,9 @@
       <c r="C31" s="2">
         <v>1.0</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="2">
+        <v>100.0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
@@ -903,7 +945,9 @@
       <c r="C32" s="2">
         <v>1.0</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="2">
+        <v>100.0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3"/>
@@ -913,7 +957,9 @@
       <c r="C33" s="2">
         <v>1.0</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="2">
+        <v>115.0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
@@ -923,7 +969,7 @@
         <v>66</v>
       </c>
       <c r="C34" s="2">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D34" s="4"/>
     </row>
@@ -935,7 +981,7 @@
         <v>68</v>
       </c>
       <c r="C35" s="2">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="D35" s="4"/>
     </row>
